--- a/data/gold/results/scenarios/health_only/full_results_tables.xlsx
+++ b/data/gold/results/scenarios/health_only/full_results_tables.xlsx
@@ -462,19 +462,19 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>151.0459394682156</v>
+        <v>324.0482157843126</v>
       </c>
       <c r="C2">
-        <v>154.2436259548418</v>
+        <v>104.5489864981368</v>
       </c>
       <c r="D2">
-        <v>4.866574284988694</v>
+        <v>14.98956579443057</v>
       </c>
       <c r="E2">
-        <v>434.2729075850427</v>
+        <v>1180.51482380909</v>
       </c>
       <c r="F2">
-        <v>67.23904457055977</v>
+        <v>25.31270961133194</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -482,19 +482,19 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>152.9978405420102</v>
+        <v>55.3874767458823</v>
       </c>
       <c r="C3">
-        <v>10.73133354957847</v>
+        <v>22.6598231313999</v>
       </c>
       <c r="D3">
-        <v>0.1453369591938662</v>
+        <v>0.2162945346307986</v>
       </c>
       <c r="E3">
-        <v>5.034453117991572</v>
+        <v>11.01736563224569</v>
       </c>
       <c r="F3">
-        <v>6.992289812544271</v>
+        <v>0.5474048216673434</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -502,7 +502,7 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>606.2380000000001</v>
+        <v>627.294307534464</v>
       </c>
       <c r="C4">
         <v>27.5319</v>
@@ -522,19 +522,19 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>930.7011963201837</v>
+        <v>189.5121042550483</v>
       </c>
       <c r="C5">
-        <v>804.3074869888835</v>
+        <v>164.9347266466416</v>
       </c>
       <c r="D5">
-        <v>6.630688018574393</v>
+        <v>2.466656624513217</v>
       </c>
       <c r="E5">
-        <v>536.9549491094017</v>
+        <v>124.0093093430114</v>
       </c>
       <c r="F5">
-        <v>234.9765223884554</v>
+        <v>7.488641848449986</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -542,7 +542,7 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>142.1847557754865</v>
+        <v>131.0762816237094</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -554,7 +554,7 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>45.1</v>
+        <v>42.75704592555413</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -562,19 +562,19 @@
         <v>11</v>
       </c>
       <c r="B7">
-        <v>1557.743923257221</v>
+        <v>1665.962465107012</v>
       </c>
       <c r="C7">
-        <v>3328.080008187533</v>
+        <v>2100.22554877125</v>
       </c>
       <c r="D7">
-        <v>22.87291155310106</v>
+        <v>54.91780859221199</v>
       </c>
       <c r="E7">
-        <v>1873.121878063462</v>
+        <v>1972.977223547686</v>
       </c>
       <c r="F7">
-        <v>792.2907711544839</v>
+        <v>97.43642436380381</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -582,19 +582,19 @@
         <v>12</v>
       </c>
       <c r="B8">
-        <v>224.7062368943004</v>
+        <v>461.8982492447063</v>
       </c>
       <c r="C8">
-        <v>225.3940916051857</v>
+        <v>272.768433428783</v>
       </c>
       <c r="D8">
-        <v>2.301769693324651</v>
+        <v>7.992110459531147</v>
       </c>
       <c r="E8">
-        <v>234.9024092177114</v>
+        <v>517.0528477636774</v>
       </c>
       <c r="F8">
-        <v>51.90589081900845</v>
+        <v>22.15487036495229</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -602,19 +602,19 @@
         <v>13</v>
       </c>
       <c r="B9">
-        <v>256.0616136208282</v>
+        <v>444.8282684352791</v>
       </c>
       <c r="C9">
-        <v>124.7390154898849</v>
+        <v>97.73626305353363</v>
       </c>
       <c r="D9">
-        <v>0.5778664944715616</v>
+        <v>1.882057622749604</v>
       </c>
       <c r="E9">
-        <v>64.35033314043307</v>
+        <v>135.0667377025332</v>
       </c>
       <c r="F9">
-        <v>13.83268538950556</v>
+        <v>6.378269348035411</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -622,19 +622,19 @@
         <v>14</v>
       </c>
       <c r="B10">
-        <v>383.4781431117855</v>
+        <v>219.0358593567161</v>
       </c>
       <c r="C10">
-        <v>448.2683589260894</v>
+        <v>894.4537108856917</v>
       </c>
       <c r="D10">
-        <v>1.318527992807899</v>
+        <v>1.766859403621039</v>
       </c>
       <c r="E10">
-        <v>263.650208624463</v>
+        <v>154.9996544430525</v>
       </c>
       <c r="F10">
-        <v>141.3410475383024</v>
+        <v>26.85786278951561</v>
       </c>
     </row>
   </sheetData>
@@ -672,19 +672,19 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>3.428842995047995</v>
+        <v>7.867074896778869</v>
       </c>
       <c r="C2">
-        <v>3.010632829975982</v>
+        <v>2.837258504716094</v>
       </c>
       <c r="D2">
-        <v>12.50893826125776</v>
+        <v>17.75542554870346</v>
       </c>
       <c r="E2">
-        <v>12.72005829513396</v>
+        <v>28.81110157936517</v>
       </c>
       <c r="F2">
-        <v>4.967136355146916</v>
+        <v>11.05680888431715</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -692,19 +692,19 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>3.473152443865156</v>
+        <v>1.344668498941781</v>
       </c>
       <c r="C3">
-        <v>0.2094615248687329</v>
+        <v>0.6149440377030592</v>
       </c>
       <c r="D3">
-        <v>0.3735710056338398</v>
+        <v>0.2562049867819067</v>
       </c>
       <c r="E3">
-        <v>0.1474615064086889</v>
+        <v>0.2688847560113061</v>
       </c>
       <c r="F3">
-        <v>0.5165400126583465</v>
+        <v>0.2391111259309804</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -712,16 +712,16 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>13.76200463878953</v>
+        <v>15.22912659078301</v>
       </c>
       <c r="C4">
-        <v>0.5373864981356388</v>
+        <v>0.7471628376558693</v>
       </c>
       <c r="D4">
-        <v>0.4911993451122079</v>
+        <v>0.2263615817089202</v>
       </c>
       <c r="E4">
-        <v>0.05250024141497557</v>
+        <v>0.0437444896322669</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -732,19 +732,19 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>21.12753436948085</v>
+        <v>4.60087679980618</v>
       </c>
       <c r="C5">
-        <v>15.69902490773365</v>
+        <v>4.476011404563428</v>
       </c>
       <c r="D5">
-        <v>17.04337840066513</v>
+        <v>2.92180164865305</v>
       </c>
       <c r="E5">
-        <v>15.72766372305819</v>
+        <v>3.026514141296551</v>
       </c>
       <c r="F5">
-        <v>17.35837316571159</v>
+        <v>3.271103054267374</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -752,7 +752,7 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>3.227688248752803</v>
+        <v>3.182202136892377</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -764,7 +764,7 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>3.331663188373305</v>
+        <v>18.6766447573507</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -772,19 +772,19 @@
         <v>11</v>
       </c>
       <c r="B7">
-        <v>35.36182010680967</v>
+        <v>40.44537463814574</v>
       </c>
       <c r="C7">
-        <v>64.95974709755325</v>
+        <v>56.99608384228051</v>
       </c>
       <c r="D7">
-        <v>58.79204173570222</v>
+        <v>65.05118794830366</v>
       </c>
       <c r="E7">
-        <v>54.8646232972574</v>
+        <v>48.15157425807882</v>
       </c>
       <c r="F7">
-        <v>58.52873606969605</v>
+        <v>42.56106671723137</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -792,19 +792,19 @@
         <v>12</v>
       </c>
       <c r="B8">
-        <v>5.100980595911673</v>
+        <v>11.21372667553213</v>
       </c>
       <c r="C8">
-        <v>4.399396394298036</v>
+        <v>7.402410903119494</v>
       </c>
       <c r="D8">
-        <v>5.916419497436925</v>
+        <v>9.466806723243721</v>
       </c>
       <c r="E8">
-        <v>6.880402361576226</v>
+        <v>12.61895388213136</v>
       </c>
       <c r="F8">
-        <v>3.834433385840673</v>
+        <v>9.677437589393243</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -812,19 +812,19 @@
         <v>13</v>
       </c>
       <c r="B9">
-        <v>5.812768441545681</v>
+        <v>10.7993105146861</v>
       </c>
       <c r="C9">
-        <v>2.434741616633666</v>
+        <v>2.652374287461406</v>
       </c>
       <c r="D9">
-        <v>1.485335654875554</v>
+        <v>2.229333021208428</v>
       </c>
       <c r="E9">
-        <v>1.884851609577571</v>
+        <v>3.29637664979501</v>
       </c>
       <c r="F9">
-        <v>1.021859173138912</v>
+        <v>2.786082812815661</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -832,19 +832,19 @@
         <v>14</v>
       </c>
       <c r="B10">
-        <v>8.705208159796628</v>
+        <v>5.317639248433808</v>
       </c>
       <c r="C10">
-        <v>8.749609130801028</v>
+        <v>24.27375418250015</v>
       </c>
       <c r="D10">
-        <v>3.389116099316348</v>
+        <v>2.092878541396849</v>
       </c>
       <c r="E10">
-        <v>7.722438965572964</v>
+        <v>3.7828502436895</v>
       </c>
       <c r="F10">
-        <v>10.44125864943422</v>
+        <v>11.73174505869352</v>
       </c>
     </row>
   </sheetData>
@@ -882,19 +882,19 @@
         <v>16</v>
       </c>
       <c r="B2">
-        <v>267.13790816009</v>
+        <v>506.0058571376234</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>40.75597665441908</v>
       </c>
       <c r="D2">
-        <v>29.27386916832974</v>
+        <v>72.12182911225848</v>
       </c>
       <c r="E2">
-        <v>3186.059192440568</v>
+        <v>4052.534475515813</v>
       </c>
       <c r="F2">
-        <v>137.4325731907398</v>
+        <v>38.5683318595245</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -902,19 +902,19 @@
         <v>17</v>
       </c>
       <c r="B3">
-        <v>1186.404119525121</v>
+        <v>355.3464638730131</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>8.100082208865288</v>
       </c>
       <c r="D3">
-        <v>2.145879543825009</v>
+        <v>2.935991581565479</v>
       </c>
       <c r="E3">
-        <v>1.34720008484481E-05</v>
+        <v>1.816046814882257</v>
       </c>
       <c r="F3">
-        <v>33.93755066505819</v>
+        <v>12.06577150988851</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -922,19 +922,19 @@
         <v>18</v>
       </c>
       <c r="B4">
-        <v>385.3164891937948</v>
+        <v>666.1582587976729</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>16.75250719820433</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>0.05921830450956449</v>
       </c>
       <c r="E4">
-        <v>11.64020139234707</v>
+        <v>1.577388808603074</v>
       </c>
       <c r="F4">
-        <v>9.796821889342782</v>
+        <v>11.45771453775908</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -942,19 +942,19 @@
         <v>19</v>
       </c>
       <c r="B5">
-        <v>1.006163911106387</v>
+        <v>94.64261947292124</v>
       </c>
       <c r="C5">
-        <v>5095.763920701996</v>
+        <v>3102.836062876452</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>0.02786273299312532</v>
       </c>
       <c r="E5">
-        <v>0.04454971339956332</v>
+        <v>0.4552911524909666</v>
       </c>
       <c r="F5">
-        <v>837.7927188704354</v>
+        <v>0.2700544599679646</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -962,7 +962,7 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>142.1847557754865</v>
+        <v>131.0762816237094</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -974,7 +974,7 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>45.1</v>
+        <v>42.75704592555413</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -982,19 +982,19 @@
         <v>20</v>
       </c>
       <c r="B7">
-        <v>318.7799070656467</v>
+        <v>412.2509312106818</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>308.3845277532511</v>
       </c>
       <c r="D7">
-        <v>3.332783536787012</v>
+        <v>6.695764980135035</v>
       </c>
       <c r="E7">
-        <v>8.31371857975028</v>
+        <v>0.6578225074997397</v>
       </c>
       <c r="F7">
-        <v>90.87243858412553</v>
+        <v>66.40267860617962</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1002,19 +1002,19 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>371.6261253404833</v>
+        <v>575.7717046858004</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>17.46581803139808</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>0.02747892639668744</v>
       </c>
       <c r="E8">
-        <v>49.22272275191975</v>
+        <v>3.663846212330291</v>
       </c>
       <c r="F8">
-        <v>1.546066334411537</v>
+        <v>1.86132003592239</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1022,19 +1022,19 @@
         <v>14</v>
       </c>
       <c r="B9">
-        <v>1732.702180018301</v>
+        <v>1377.79111128571</v>
       </c>
       <c r="C9">
-        <v>27.5319</v>
+        <v>190.5644176928446</v>
       </c>
       <c r="D9">
-        <v>4.152242747520369</v>
+        <v>2.554307393829987</v>
       </c>
       <c r="E9">
-        <v>158.799140508517</v>
+        <v>36.72549122967252</v>
       </c>
       <c r="F9">
-        <v>197.2000821387473</v>
+        <v>55.55031213851447</v>
       </c>
     </row>
   </sheetData>
@@ -1072,19 +1072,19 @@
         <v>16</v>
       </c>
       <c r="B2">
-        <v>6.064207673051992</v>
+        <v>12.28454835548328</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>1.106038855602125</v>
       </c>
       <c r="D2">
-        <v>75.24492603026701</v>
+        <v>85.4296772035127</v>
       </c>
       <c r="E2">
-        <v>93.32117650386746</v>
+        <v>98.90429164729183</v>
       </c>
       <c r="F2">
-        <v>10.15252871359218</v>
+        <v>16.84697849047237</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1092,19 +1092,19 @@
         <v>17</v>
       </c>
       <c r="B3">
-        <v>26.93216030071314</v>
+        <v>8.626917567894392</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>0.2198206592506007</v>
       </c>
       <c r="D3">
-        <v>5.515722797574714</v>
+        <v>3.477737824632318</v>
       </c>
       <c r="E3">
-        <v>3.946012591420897E-07</v>
+        <v>0.04432160291526909</v>
       </c>
       <c r="F3">
-        <v>2.507061823821025</v>
+        <v>5.27043258802099</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1112,19 +1112,19 @@
         <v>18</v>
       </c>
       <c r="B4">
-        <v>8.746939834994018</v>
+        <v>16.17264548852609</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>0.4546308397190433</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>0.070145207090034</v>
       </c>
       <c r="E4">
-        <v>0.3409469890745127</v>
+        <v>0.03849702543181829</v>
       </c>
       <c r="F4">
-        <v>0.7237186441634841</v>
+        <v>5.00482808202998</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1132,19 +1132,19 @@
         <v>19</v>
       </c>
       <c r="B5">
-        <v>0.02284058803972816</v>
+        <v>2.297684540612916</v>
       </c>
       <c r="C5">
-        <v>99.46261350186435</v>
+        <v>84.20500573951442</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>0.03300393674022586</v>
       </c>
       <c r="E5">
-        <v>0.001304882118079139</v>
+        <v>0.01111162636677302</v>
       </c>
       <c r="F5">
-        <v>61.89009226048364</v>
+        <v>0.1179621067073167</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1152,7 +1152,7 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>3.227688248752805</v>
+        <v>3.182202136892376</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1164,7 +1164,7 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>3.331663188373302</v>
+        <v>18.67664475735069</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1172,19 +1172,19 @@
         <v>20</v>
       </c>
       <c r="B7">
-        <v>7.236515295627012</v>
+        <v>10.00841477942269</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>8.368963233386888</v>
       </c>
       <c r="D7">
-        <v>8.566515388124168</v>
+        <v>7.93126086684753</v>
       </c>
       <c r="E7">
-        <v>0.2435127385031566</v>
+        <v>0.01605451342289345</v>
       </c>
       <c r="F7">
-        <v>6.713001296417844</v>
+        <v>29.00526012539476</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1192,19 +1192,19 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>8.436159496486715</v>
+        <v>13.97828750035203</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>0.4739887244367605</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>0.03254931053279523</v>
       </c>
       <c r="E8">
-        <v>1.44175676611147</v>
+        <v>0.08941814474977848</v>
       </c>
       <c r="F8">
-        <v>0.1142122459676755</v>
+        <v>0.8130405723348901</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1212,19 +1212,19 @@
         <v>14</v>
       </c>
       <c r="B9">
-        <v>39.3334885623346</v>
+        <v>33.44929963081623</v>
       </c>
       <c r="C9">
-        <v>0.537386498135639</v>
+        <v>5.171551948090187</v>
       </c>
       <c r="D9">
-        <v>10.67283578403412</v>
+        <v>3.025625650644404</v>
       </c>
       <c r="E9">
-        <v>4.651301725724044</v>
+        <v>0.8963054398216471</v>
       </c>
       <c r="F9">
-        <v>14.56772182718084</v>
+        <v>24.26485327768899</v>
       </c>
     </row>
   </sheetData>
@@ -1262,7 +1262,7 @@
         <v>14</v>
       </c>
       <c r="B2">
-        <v>246.6378</v>
+        <v>255.2290121415143</v>
       </c>
       <c r="C2">
         <v>27.5319</v>
@@ -1282,19 +1282,19 @@
         <v>22</v>
       </c>
       <c r="B3">
-        <v>395.0551774073508</v>
+        <v>275.6215200200326</v>
       </c>
       <c r="C3">
-        <v>364.9541978952167</v>
+        <v>302.3295151757029</v>
       </c>
       <c r="D3">
-        <v>5.321674893003141</v>
+        <v>25.68451063140679</v>
       </c>
       <c r="E3">
-        <v>112.1758219650602</v>
+        <v>264.9693351177935</v>
       </c>
       <c r="F3">
-        <v>9.639959248208633</v>
+        <v>2.40239874828681</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1302,19 +1302,19 @@
         <v>23</v>
       </c>
       <c r="B4">
-        <v>541.2447142164228</v>
+        <v>1358.876859602191</v>
       </c>
       <c r="C4">
-        <v>425.8866784891411</v>
+        <v>839.3877221140265</v>
       </c>
       <c r="D4">
-        <v>3.748270572269079</v>
+        <v>11.79057839470132</v>
       </c>
       <c r="E4">
-        <v>864.5865119399796</v>
+        <v>1438.570729621462</v>
       </c>
       <c r="F4">
-        <v>120.356775026513</v>
+        <v>62.63562890061036</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1322,19 +1322,19 @@
         <v>24</v>
       </c>
       <c r="B5">
-        <v>1799.274296845495</v>
+        <v>707.4941618107144</v>
       </c>
       <c r="C5">
-        <v>2433.088378956372</v>
+        <v>653.4677613473955</v>
       </c>
       <c r="D5">
-        <v>21.3165108144331</v>
+        <v>33.71758374884114</v>
       </c>
       <c r="E5">
-        <v>800.2951427865283</v>
+        <v>901.2147631282047</v>
       </c>
       <c r="F5">
-        <v>380.354296982323</v>
+        <v>24.57999250844659</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1342,19 +1342,19 @@
         <v>25</v>
       </c>
       <c r="B6">
-        <v>252.9701712759522</v>
+        <v>265.3842332141264</v>
       </c>
       <c r="C6">
-        <v>1518.684592261697</v>
+        <v>137.6969965221313</v>
       </c>
       <c r="D6">
-        <v>5.596280069563865</v>
+        <v>6.021847351322965</v>
       </c>
       <c r="E6">
-        <v>979.6478564126198</v>
+        <v>455.4903580375011</v>
       </c>
       <c r="F6">
-        <v>604.1932369651104</v>
+        <v>8.339925140300817</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1362,19 +1362,19 @@
         <v>26</v>
       </c>
       <c r="B7">
-        <v>84.62209163275757</v>
+        <v>163.3904247022428</v>
       </c>
       <c r="C7">
-        <v>81.10674889625183</v>
+        <v>83.18852704077868</v>
       </c>
       <c r="D7">
-        <v>2.107301645411055</v>
+        <v>3.467258245775705</v>
       </c>
       <c r="E7">
-        <v>522.0842877891183</v>
+        <v>750.6404493841055</v>
       </c>
       <c r="F7">
-        <v>48.59333271375147</v>
+        <v>11.63803272781293</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1382,19 +1382,19 @@
         <v>27</v>
       </c>
       <c r="B8">
-        <v>1085.35339761205</v>
+        <v>1093.047016596306</v>
       </c>
       <c r="C8">
-        <v>272.0433242033174</v>
+        <v>1641.2569702154</v>
       </c>
       <c r="D8">
-        <v>0.6236370017818897</v>
+        <v>3.54957465964045</v>
       </c>
       <c r="E8">
-        <v>133.4975179651968</v>
+        <v>284.7523269522258</v>
       </c>
       <c r="F8">
-        <v>190.5406507369543</v>
+        <v>119.3372510478532</v>
       </c>
     </row>
   </sheetData>
@@ -1432,16 +1432,16 @@
         <v>14</v>
       </c>
       <c r="B2">
-        <v>5.598841622763416</v>
+        <v>6.196317882782743</v>
       </c>
       <c r="C2">
-        <v>0.5373864981356389</v>
+        <v>0.7471628376558698</v>
       </c>
       <c r="D2">
-        <v>0.491199345112208</v>
+        <v>0.2263615817089201</v>
       </c>
       <c r="E2">
-        <v>0.05250024141497561</v>
+        <v>0.04374448963226693</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -1452,19 +1452,19 @@
         <v>22</v>
       </c>
       <c r="B3">
-        <v>8.96801451584656</v>
+        <v>6.691396636495861</v>
       </c>
       <c r="C3">
-        <v>7.123426221467152</v>
+        <v>8.204641832412639</v>
       </c>
       <c r="D3">
-        <v>13.67871911220943</v>
+        <v>30.42379095732505</v>
       </c>
       <c r="E3">
-        <v>3.285682734930251</v>
+        <v>6.466719668003226</v>
       </c>
       <c r="F3">
-        <v>0.7121307619661967</v>
+        <v>1.049388399408588</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1472,19 +1472,19 @@
         <v>23</v>
       </c>
       <c r="B4">
-        <v>12.28661394991197</v>
+        <v>32.99010921604846</v>
       </c>
       <c r="C4">
-        <v>8.312748148725598</v>
+        <v>22.77936910813321</v>
       </c>
       <c r="D4">
-        <v>9.634474361077618</v>
+        <v>13.96616417942235</v>
       </c>
       <c r="E4">
-        <v>25.32414673118758</v>
+        <v>35.10909527293502</v>
       </c>
       <c r="F4">
-        <v>8.891091725657663</v>
+        <v>27.35978047142851</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1492,19 +1492,19 @@
         <v>24</v>
       </c>
       <c r="B5">
-        <v>40.8447197629355</v>
+        <v>17.17617715168463</v>
       </c>
       <c r="C5">
-        <v>47.49068693486041</v>
+        <v>17.73385879234447</v>
       </c>
       <c r="D5">
-        <v>54.79150262756064</v>
+        <v>39.93911872731899</v>
       </c>
       <c r="E5">
-        <v>23.44102220460003</v>
+        <v>21.99463281751152</v>
       </c>
       <c r="F5">
-        <v>28.09783613737499</v>
+        <v>10.73675176292359</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1512,19 +1512,19 @@
         <v>25</v>
       </c>
       <c r="B6">
-        <v>5.742590650165511</v>
+        <v>6.442861084936225</v>
       </c>
       <c r="C6">
-        <v>29.64272697518384</v>
+        <v>3.736831771805289</v>
       </c>
       <c r="D6">
-        <v>14.38455837380572</v>
+        <v>7.132992628232013</v>
       </c>
       <c r="E6">
-        <v>28.69434778136906</v>
+        <v>11.11648808567787</v>
       </c>
       <c r="F6">
-        <v>44.63344492817662</v>
+        <v>3.642950904968953</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1532,19 +1532,19 @@
         <v>26</v>
       </c>
       <c r="B7">
-        <v>1.920977598887043</v>
+        <v>3.966708180873373</v>
       </c>
       <c r="C7">
-        <v>1.58309712604373</v>
+        <v>2.257576699181686</v>
       </c>
       <c r="D7">
-        <v>5.416562994138088</v>
+        <v>4.107033284704785</v>
       </c>
       <c r="E7">
-        <v>15.29209503899482</v>
+        <v>18.3197854026128</v>
       </c>
       <c r="F7">
-        <v>3.589725450172546</v>
+        <v>5.083592615594529</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1552,19 +1552,19 @@
         <v>27</v>
       </c>
       <c r="B8">
-        <v>24.63824189949</v>
+        <v>26.5364298471787</v>
       </c>
       <c r="C8">
-        <v>5.309928095583633</v>
+        <v>44.54055895846685</v>
       </c>
       <c r="D8">
-        <v>1.602983186096312</v>
+        <v>4.204538641287881</v>
       </c>
       <c r="E8">
-        <v>3.910205267503277</v>
+        <v>6.949534263627273</v>
       </c>
       <c r="F8">
-        <v>14.075770996652</v>
+        <v>52.12753584567582</v>
       </c>
     </row>
   </sheetData>

--- a/data/gold/results/scenarios/health_only/full_results_tables.xlsx
+++ b/data/gold/results/scenarios/health_only/full_results_tables.xlsx
@@ -505,13 +505,13 @@
         <v>627.294307534464</v>
       </c>
       <c r="C4">
-        <v>27.5319</v>
+        <v>25.6351</v>
       </c>
       <c r="D4">
-        <v>0.1911</v>
+        <v>0.1776</v>
       </c>
       <c r="E4">
-        <v>1.7924</v>
+        <v>1.6692</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -675,13 +675,13 @@
         <v>7.867074896778869</v>
       </c>
       <c r="C2">
-        <v>2.837258504716094</v>
+        <v>2.838719750057773</v>
       </c>
       <c r="D2">
-        <v>17.75542554870346</v>
+        <v>17.75826527406787</v>
       </c>
       <c r="E2">
-        <v>28.81110157936517</v>
+        <v>28.81196788681395</v>
       </c>
       <c r="F2">
         <v>11.05680888431715</v>
@@ -695,13 +695,13 @@
         <v>1.344668498941781</v>
       </c>
       <c r="C3">
-        <v>0.6149440377030592</v>
+        <v>0.6152607462824831</v>
       </c>
       <c r="D3">
-        <v>0.2562049867819067</v>
+        <v>0.2562459630906669</v>
       </c>
       <c r="E3">
-        <v>0.2688847560113061</v>
+        <v>0.2688928409804405</v>
       </c>
       <c r="F3">
         <v>0.2391111259309804</v>
@@ -715,13 +715,13 @@
         <v>15.22912659078301</v>
       </c>
       <c r="C4">
-        <v>0.7471628376558693</v>
+        <v>0.6960456251386323</v>
       </c>
       <c r="D4">
-        <v>0.2263615817089202</v>
+        <v>0.2104042209045364</v>
       </c>
       <c r="E4">
-        <v>0.0437444896322669</v>
+        <v>0.04073895204593153</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -735,13 +735,13 @@
         <v>4.60087679980618</v>
       </c>
       <c r="C5">
-        <v>4.476011404563428</v>
+        <v>4.478316640693076</v>
       </c>
       <c r="D5">
-        <v>2.92180164865305</v>
+        <v>2.922268948872281</v>
       </c>
       <c r="E5">
-        <v>3.026514141296551</v>
+        <v>3.026605144125347</v>
       </c>
       <c r="F5">
         <v>3.271103054267374</v>
@@ -775,13 +775,13 @@
         <v>40.44537463814574</v>
       </c>
       <c r="C7">
-        <v>56.99608384228051</v>
+        <v>57.02543797475383</v>
       </c>
       <c r="D7">
-        <v>65.05118794830366</v>
+        <v>65.06159195173885</v>
       </c>
       <c r="E7">
-        <v>48.15157425807882</v>
+        <v>48.15302210509485</v>
       </c>
       <c r="F7">
         <v>42.56106671723137</v>
@@ -795,13 +795,13 @@
         <v>11.21372667553213</v>
       </c>
       <c r="C8">
-        <v>7.402410903119494</v>
+        <v>7.406223294000127</v>
       </c>
       <c r="D8">
-        <v>9.466806723243721</v>
+        <v>9.468320803044186</v>
       </c>
       <c r="E8">
-        <v>12.61895388213136</v>
+        <v>12.61933331551449</v>
       </c>
       <c r="F8">
         <v>9.677437589393243</v>
@@ -815,13 +815,13 @@
         <v>10.7993105146861</v>
       </c>
       <c r="C9">
-        <v>2.652374287461406</v>
+        <v>2.653740313703111</v>
       </c>
       <c r="D9">
-        <v>2.229333021208428</v>
+        <v>2.229689571013933</v>
       </c>
       <c r="E9">
-        <v>3.29637664979501</v>
+        <v>3.296475766992519</v>
       </c>
       <c r="F9">
         <v>2.786082812815661</v>
@@ -835,13 +835,13 @@
         <v>5.317639248433808</v>
       </c>
       <c r="C10">
-        <v>24.27375418250015</v>
+        <v>24.28625565537099</v>
       </c>
       <c r="D10">
-        <v>2.092878541396849</v>
+        <v>2.093213267267672</v>
       </c>
       <c r="E10">
-        <v>3.7828502436895</v>
+        <v>3.782963988432466</v>
       </c>
       <c r="F10">
         <v>11.73174505869352</v>
@@ -1025,13 +1025,13 @@
         <v>1377.79111128571</v>
       </c>
       <c r="C9">
-        <v>190.5644176928446</v>
+        <v>188.6676176928446</v>
       </c>
       <c r="D9">
-        <v>2.554307393829987</v>
+        <v>2.540807393829987</v>
       </c>
       <c r="E9">
-        <v>36.72549122967252</v>
+        <v>36.60229122967252</v>
       </c>
       <c r="F9">
         <v>55.55031213851447</v>
@@ -1075,13 +1075,13 @@
         <v>12.28454835548328</v>
       </c>
       <c r="C2">
-        <v>1.106038855602125</v>
+        <v>1.106608487915422</v>
       </c>
       <c r="D2">
-        <v>85.4296772035127</v>
+        <v>85.44334045368728</v>
       </c>
       <c r="E2">
-        <v>98.90429164729183</v>
+        <v>98.90726555387204</v>
       </c>
       <c r="F2">
         <v>16.84697849047237</v>
@@ -1095,13 +1095,13 @@
         <v>8.626917567894392</v>
       </c>
       <c r="C3">
-        <v>0.2198206592506007</v>
+        <v>0.2199338713226769</v>
       </c>
       <c r="D3">
-        <v>3.477737824632318</v>
+        <v>3.478294038860148</v>
       </c>
       <c r="E3">
-        <v>0.04432160291526909</v>
+        <v>0.04432293560068001</v>
       </c>
       <c r="F3">
         <v>5.27043258802099</v>
@@ -1115,13 +1115,13 @@
         <v>16.17264548852609</v>
       </c>
       <c r="C4">
-        <v>0.4546308397190433</v>
+        <v>0.4548649837688784</v>
       </c>
       <c r="D4">
-        <v>0.070145207090034</v>
+        <v>0.07015642580868532</v>
       </c>
       <c r="E4">
-        <v>0.03849702543181829</v>
+        <v>0.03849818298075114</v>
       </c>
       <c r="F4">
         <v>5.00482808202998</v>
@@ -1135,13 +1135,13 @@
         <v>2.297684540612916</v>
       </c>
       <c r="C5">
-        <v>84.20500573951442</v>
+        <v>84.24837301541768</v>
       </c>
       <c r="D5">
-        <v>0.03300393674022586</v>
+        <v>0.03300921524600031</v>
       </c>
       <c r="E5">
-        <v>0.01111162636677302</v>
+        <v>0.01111196047703475</v>
       </c>
       <c r="F5">
         <v>0.1179621067073167</v>
@@ -1175,13 +1175,13 @@
         <v>10.00841477942269</v>
       </c>
       <c r="C7">
-        <v>8.368963233386888</v>
+        <v>8.373273418207601</v>
       </c>
       <c r="D7">
-        <v>7.93126086684753</v>
+        <v>7.932529358137336</v>
       </c>
       <c r="E7">
-        <v>0.01605451342289345</v>
+        <v>0.0160549961584989</v>
       </c>
       <c r="F7">
         <v>29.00526012539476</v>
@@ -1195,13 +1195,13 @@
         <v>13.97828750035203</v>
       </c>
       <c r="C8">
-        <v>0.4739887244367605</v>
+        <v>0.4742328381875663</v>
       </c>
       <c r="D8">
-        <v>0.03254931053279523</v>
+        <v>0.03255451632763583</v>
       </c>
       <c r="E8">
-        <v>0.08941814474977848</v>
+        <v>0.08942083342187383</v>
       </c>
       <c r="F8">
         <v>0.8130405723348901</v>
@@ -1215,13 +1215,13 @@
         <v>33.44929963081623</v>
       </c>
       <c r="C9">
-        <v>5.171551948090187</v>
+        <v>5.122713385180185</v>
       </c>
       <c r="D9">
-        <v>3.025625650644404</v>
+        <v>3.010115991932906</v>
       </c>
       <c r="E9">
-        <v>0.8963054398216471</v>
+        <v>0.893325537489127</v>
       </c>
       <c r="F9">
         <v>24.26485327768899</v>
@@ -1262,16 +1262,16 @@
         <v>14</v>
       </c>
       <c r="B2">
-        <v>255.2290121415143</v>
+        <v>255.2290104137513</v>
       </c>
       <c r="C2">
-        <v>27.5319</v>
+        <v>25.6351</v>
       </c>
       <c r="D2">
-        <v>0.1911</v>
+        <v>0.1776</v>
       </c>
       <c r="E2">
-        <v>1.7924</v>
+        <v>1.6692</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -1382,7 +1382,7 @@
         <v>27</v>
       </c>
       <c r="B8">
-        <v>1093.047016596306</v>
+        <v>1093.047018324069</v>
       </c>
       <c r="C8">
         <v>1641.2569702154</v>
@@ -1432,16 +1432,16 @@
         <v>14</v>
       </c>
       <c r="B2">
-        <v>6.196317882782743</v>
+        <v>6.196317840837009</v>
       </c>
       <c r="C2">
-        <v>0.7471628376558698</v>
+        <v>0.6960456251386327</v>
       </c>
       <c r="D2">
-        <v>0.2263615817089201</v>
+        <v>0.2104042209045364</v>
       </c>
       <c r="E2">
-        <v>0.04374448963226693</v>
+        <v>0.04073895204593157</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -1452,16 +1452,16 @@
         <v>22</v>
       </c>
       <c r="B3">
-        <v>6.691396636495861</v>
+        <v>6.691396636495862</v>
       </c>
       <c r="C3">
-        <v>8.204641832412639</v>
+        <v>8.208867388398401</v>
       </c>
       <c r="D3">
-        <v>30.42379095732505</v>
+        <v>30.42865680583012</v>
       </c>
       <c r="E3">
-        <v>6.466719668003226</v>
+        <v>6.466914112752314</v>
       </c>
       <c r="F3">
         <v>1.049388399408588</v>
@@ -1472,16 +1472,16 @@
         <v>23</v>
       </c>
       <c r="B4">
-        <v>32.99010921604846</v>
+        <v>32.99010921604847</v>
       </c>
       <c r="C4">
-        <v>22.77936910813321</v>
+        <v>22.79110094255729</v>
       </c>
       <c r="D4">
-        <v>13.96616417942235</v>
+        <v>13.96839786684116</v>
       </c>
       <c r="E4">
-        <v>35.10909527293502</v>
+        <v>35.110150951791</v>
       </c>
       <c r="F4">
         <v>27.35978047142851</v>
@@ -1492,16 +1492,16 @@
         <v>24</v>
       </c>
       <c r="B5">
-        <v>17.17617715168463</v>
+        <v>17.17617715168464</v>
       </c>
       <c r="C5">
-        <v>17.73385879234447</v>
+        <v>17.74299208721599</v>
       </c>
       <c r="D5">
-        <v>39.93911872731899</v>
+        <v>39.94550641586924</v>
       </c>
       <c r="E5">
-        <v>21.99463281751152</v>
+        <v>21.99529416377037</v>
       </c>
       <c r="F5">
         <v>10.73675176292359</v>
@@ -1512,16 +1512,16 @@
         <v>25</v>
       </c>
       <c r="B6">
-        <v>6.442861084936225</v>
+        <v>6.442861084936226</v>
       </c>
       <c r="C6">
-        <v>3.736831771805289</v>
+        <v>3.738756315518917</v>
       </c>
       <c r="D6">
-        <v>7.132992628232013</v>
+        <v>7.134133447979474</v>
       </c>
       <c r="E6">
-        <v>11.11648808567787</v>
+        <v>11.11682234212434</v>
       </c>
       <c r="F6">
         <v>3.642950904968953</v>
@@ -1532,16 +1532,16 @@
         <v>26</v>
       </c>
       <c r="B7">
-        <v>3.966708180873373</v>
+        <v>3.966708180873374</v>
       </c>
       <c r="C7">
-        <v>2.257576699181686</v>
+        <v>2.258739396704551</v>
       </c>
       <c r="D7">
-        <v>4.107033284704785</v>
+        <v>4.107690145705331</v>
       </c>
       <c r="E7">
-        <v>18.3197854026128</v>
+        <v>18.3203362516149</v>
       </c>
       <c r="F7">
         <v>5.083592615594529</v>
@@ -1552,16 +1552,16 @@
         <v>27</v>
       </c>
       <c r="B8">
-        <v>26.5364298471787</v>
+        <v>26.53642988912444</v>
       </c>
       <c r="C8">
-        <v>44.54055895846685</v>
+        <v>44.56349824446622</v>
       </c>
       <c r="D8">
-        <v>4.204538641287881</v>
+        <v>4.205211096870123</v>
       </c>
       <c r="E8">
-        <v>6.949534263627273</v>
+        <v>6.949743225901122</v>
       </c>
       <c r="F8">
         <v>52.12753584567582</v>
